--- a/transaction3.xlsx
+++ b/transaction3.xlsx
@@ -1,53 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\assu\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98725252-030D-4586-9AEE-46F763F1551D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>transaction_id</t>
-  </si>
-  <si>
-    <t>product_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price </t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-C09]#,##0.00;[Red]\-[$$-C09]#,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -66,35 +46,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
@@ -106,172 +141,171 @@
               <a:t>Corrected Prices</a:t>
             </a:r>
           </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>5.355</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Sheet1!$D$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>5.355</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>567</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>123</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>479</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>444</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>111</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$D$3:$D$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>6.2549999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.1550000000000002</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.4550000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.5950000000000006</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>41.354999999999997</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>63.945</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6.2549999999999999</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16.11</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.1550000000000002</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.1550000000000002</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.1550000000000002</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.1550000000000002</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7.1550000000000002</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.1550000000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A598-4F65-9C1A-90A3775FCA4C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Sheet1!$B$2:$B$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="15"/>
+                <pt idx="0">
+                  <v>1</v>
+                </pt>
+                <pt idx="1">
+                  <v>2</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>4</v>
+                </pt>
+                <pt idx="4">
+                  <v>56</v>
+                </pt>
+                <pt idx="5">
+                  <v>78</v>
+                </pt>
+                <pt idx="6">
+                  <v>90</v>
+                </pt>
+                <pt idx="7">
+                  <v>567</v>
+                </pt>
+                <pt idx="8">
+                  <v>5</v>
+                </pt>
+                <pt idx="9">
+                  <v>8</v>
+                </pt>
+                <pt idx="10">
+                  <v>9</v>
+                </pt>
+                <pt idx="11">
+                  <v>123</v>
+                </pt>
+                <pt idx="12">
+                  <v>479</v>
+                </pt>
+                <pt idx="13">
+                  <v>444</v>
+                </pt>
+                <pt idx="14">
+                  <v>111</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Sheet1!$D$3:$D$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>6.255</v>
+                </pt>
+                <pt idx="1">
+                  <v>7.155</v>
+                </pt>
+                <pt idx="2">
+                  <v>4.455</v>
+                </pt>
+                <pt idx="3">
+                  <v>8.595000000000001</v>
+                </pt>
+                <pt idx="4">
+                  <v>41.355</v>
+                </pt>
+                <pt idx="5">
+                  <v>63.945</v>
+                </pt>
+                <pt idx="6">
+                  <v>6.255</v>
+                </pt>
+                <pt idx="7">
+                  <v>16.11</v>
+                </pt>
+                <pt idx="8">
+                  <v>7.155</v>
+                </pt>
+                <pt idx="9">
+                  <v>7.155</v>
+                </pt>
+                <pt idx="10">
+                  <v>7.155</v>
+                </pt>
+                <pt idx="11">
+                  <v>7.155</v>
+                </pt>
+                <pt idx="12">
+                  <v>7.155</v>
+                </pt>
+                <pt idx="13">
+                  <v>7.155</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
@@ -283,32 +317,32 @@
                   <a:t>Product ID</a:t>
                 </a:r>
               </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="100"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
@@ -320,69 +354,133 @@
                   <a:t>Price</a:t>
                 </a:r>
               </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Corrected Prices</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sheet1'!D2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Sheet1'!$B$2:$B$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sheet1'!$D$3:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5400000" cy="2700000"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -681,240 +779,254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1025" width="11.5546875" customWidth="1"/>
+    <col width="11.5546875" customWidth="1" min="1" max="1025"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>transaction_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price </t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" s="1" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.355</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>5.95</v>
-      </c>
-      <c r="D2">
-        <v>5.3550000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="n">
         <v>6.95</v>
       </c>
-      <c r="D3">
-        <v>6.2549999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="D3" t="n">
+        <v>6.255</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>1003</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="n">
         <v>7.95</v>
       </c>
-      <c r="D4">
-        <v>7.1550000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="D4" t="n">
+        <v>7.155</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>1004</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>4.95</v>
       </c>
-      <c r="D5">
-        <v>4.4550000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="D5" t="n">
+        <v>4.455</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>1005</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>56</v>
       </c>
-      <c r="C6" s="1">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="D6">
-        <v>8.5950000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="C6" s="1" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.595000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>1006</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>78</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="n">
         <v>45.95</v>
       </c>
-      <c r="D7">
-        <v>41.354999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="D7" t="n">
+        <v>41.355</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>1007</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>90</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>71.05</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>63.945</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" t="n">
         <v>1008</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>567</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="n">
         <v>6.95</v>
       </c>
-      <c r="D9">
-        <v>6.2549999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="D9" t="n">
+        <v>6.255</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>1009</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="1">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="1" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D10" t="n">
         <v>16.11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" t="n">
         <v>1010</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="1" t="n">
         <v>7.95</v>
       </c>
-      <c r="D11">
-        <v>7.1550000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="D11" t="n">
+        <v>7.155</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>1011</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="1" t="n">
         <v>7.95</v>
       </c>
-      <c r="D12">
-        <v>7.1550000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="D12" t="n">
+        <v>7.155</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>1012</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>123</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="1" t="n">
         <v>7.95</v>
       </c>
-      <c r="D13">
-        <v>7.1550000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="D13" t="n">
+        <v>7.155</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>1013</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>479</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="1" t="n">
         <v>7.95</v>
       </c>
-      <c r="D14">
-        <v>7.1550000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="D14" t="n">
+        <v>7.155</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>1014</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>444</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="1" t="n">
         <v>7.95</v>
       </c>
-      <c r="D15">
-        <v>7.1550000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="D15" t="n">
+        <v>7.155</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>1015</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>111</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="1" t="n">
         <v>7.95</v>
       </c>
-      <c r="D16">
-        <v>7.1550000000000002</v>
+      <c r="D16" t="n">
+        <v>7.155</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
